--- a/diseases/d003/2010-2014.xlsx
+++ b/diseases/d003/2010-2014.xlsx
@@ -21378,17 +21378,15 @@
       <c r="O147" t="n">
         <v>0</v>
       </c>
+      <c r="P147" t="n">
+        <v>0</v>
+      </c>
       <c r="Q147" t="n">
         <v>0</v>
       </c>
       <c r="R147" t="n">
         <v>0</v>
       </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U147" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -21396,7 +21394,7 @@
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
@@ -21406,12 +21404,7 @@
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ147" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr">
@@ -21421,11 +21414,6 @@
       </c>
       <c r="AT147" t="n">
         <v>1</v>
-      </c>
-      <c r="AU147" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
@@ -21687,17 +21675,15 @@
       <c r="O149" t="n">
         <v>0</v>
       </c>
+      <c r="P149" t="n">
+        <v>0</v>
+      </c>
       <c r="Q149" t="n">
         <v>0</v>
       </c>
       <c r="R149" t="n">
         <v>0</v>
       </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U149" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -21705,7 +21691,7 @@
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO149" t="inlineStr">
@@ -21715,12 +21701,7 @@
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ149" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr">
@@ -21730,11 +21711,6 @@
       </c>
       <c r="AT149" t="n">
         <v>1</v>
-      </c>
-      <c r="AU149" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
@@ -21996,17 +21972,15 @@
       <c r="O151" t="n">
         <v>0</v>
       </c>
+      <c r="P151" t="n">
+        <v>0</v>
+      </c>
       <c r="Q151" t="n">
         <v>0</v>
       </c>
       <c r="R151" t="n">
         <v>0</v>
       </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U151" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -22014,7 +21988,7 @@
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
@@ -22024,12 +21998,7 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ151" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr">
@@ -22039,11 +22008,6 @@
       </c>
       <c r="AT151" t="n">
         <v>1</v>
-      </c>
-      <c r="AU151" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
@@ -22716,17 +22680,15 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
+      <c r="P156" t="n">
+        <v>0</v>
+      </c>
       <c r="Q156" t="n">
         <v>0</v>
       </c>
       <c r="R156" t="n">
         <v>0</v>
       </c>
-      <c r="S156" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U156" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -22734,7 +22696,7 @@
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
@@ -22744,12 +22706,7 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ156" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr">
@@ -22759,11 +22716,6 @@
       </c>
       <c r="AT156" t="n">
         <v>1</v>
-      </c>
-      <c r="AU156" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
@@ -23025,17 +22977,15 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
+      <c r="P158" t="n">
+        <v>0</v>
+      </c>
       <c r="Q158" t="n">
         <v>0</v>
       </c>
       <c r="R158" t="n">
         <v>0</v>
       </c>
-      <c r="S158" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U158" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -23043,7 +22993,7 @@
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO158" t="inlineStr">
@@ -23053,12 +23003,7 @@
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ158" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS158" t="inlineStr">
@@ -23068,11 +23013,6 @@
       </c>
       <c r="AT158" t="n">
         <v>1</v>
-      </c>
-      <c r="AU158" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
@@ -23334,17 +23274,15 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
+      <c r="P160" t="n">
+        <v>0</v>
+      </c>
       <c r="Q160" t="n">
         <v>0</v>
       </c>
       <c r="R160" t="n">
         <v>0</v>
       </c>
-      <c r="S160" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U160" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -23352,7 +23290,7 @@
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
@@ -23362,12 +23300,7 @@
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ160" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS160" t="inlineStr">
@@ -23377,11 +23310,6 @@
       </c>
       <c r="AT160" t="n">
         <v>1</v>
-      </c>
-      <c r="AU160" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
@@ -23643,17 +23571,15 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
+      <c r="P162" t="n">
+        <v>0</v>
+      </c>
       <c r="Q162" t="n">
         <v>0</v>
       </c>
       <c r="R162" t="n">
         <v>0</v>
       </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U162" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -23661,7 +23587,7 @@
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
@@ -23671,12 +23597,7 @@
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ162" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr">
@@ -23686,11 +23607,6 @@
       </c>
       <c r="AT162" t="n">
         <v>1</v>
-      </c>
-      <c r="AU162" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
@@ -24363,17 +24279,15 @@
       <c r="O167" t="n">
         <v>0</v>
       </c>
+      <c r="P167" t="n">
+        <v>0</v>
+      </c>
       <c r="Q167" t="n">
         <v>0</v>
       </c>
       <c r="R167" t="n">
         <v>0</v>
       </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U167" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -24381,7 +24295,7 @@
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO167" t="inlineStr">
@@ -24391,12 +24305,7 @@
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ167" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr">
@@ -24406,11 +24315,6 @@
       </c>
       <c r="AT167" t="n">
         <v>1</v>
-      </c>
-      <c r="AU167" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
@@ -24672,17 +24576,15 @@
       <c r="O169" t="n">
         <v>0</v>
       </c>
+      <c r="P169" t="n">
+        <v>0</v>
+      </c>
       <c r="Q169" t="n">
         <v>0</v>
       </c>
       <c r="R169" t="n">
         <v>0</v>
       </c>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U169" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -24690,7 +24592,7 @@
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO169" t="inlineStr">
@@ -24700,12 +24602,7 @@
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ169" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS169" t="inlineStr">
@@ -24715,11 +24612,6 @@
       </c>
       <c r="AT169" t="n">
         <v>1</v>
-      </c>
-      <c r="AU169" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
@@ -24981,17 +24873,15 @@
       <c r="O171" t="n">
         <v>0</v>
       </c>
+      <c r="P171" t="n">
+        <v>0</v>
+      </c>
       <c r="Q171" t="n">
         <v>0</v>
       </c>
       <c r="R171" t="n">
         <v>0</v>
       </c>
-      <c r="S171" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U171" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -24999,7 +24889,7 @@
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO171" t="inlineStr">
@@ -25009,12 +24899,7 @@
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ171" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS171" t="inlineStr">
@@ -25024,11 +24909,6 @@
       </c>
       <c r="AT171" t="n">
         <v>1</v>
-      </c>
-      <c r="AU171" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
@@ -25290,17 +25170,15 @@
       <c r="O173" t="n">
         <v>0</v>
       </c>
+      <c r="P173" t="n">
+        <v>0</v>
+      </c>
       <c r="Q173" t="n">
         <v>0</v>
       </c>
       <c r="R173" t="n">
         <v>0</v>
       </c>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U173" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -25308,7 +25186,7 @@
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
@@ -25318,12 +25196,7 @@
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ173" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr">
@@ -25333,11 +25206,6 @@
       </c>
       <c r="AT173" t="n">
         <v>1</v>
-      </c>
-      <c r="AU173" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
@@ -25599,17 +25467,15 @@
       <c r="O175" t="n">
         <v>0</v>
       </c>
+      <c r="P175" t="n">
+        <v>0</v>
+      </c>
       <c r="Q175" t="n">
         <v>0</v>
       </c>
       <c r="R175" t="n">
         <v>0</v>
       </c>
-      <c r="S175" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U175" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -25617,7 +25483,7 @@
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO175" t="inlineStr">
@@ -25627,12 +25493,7 @@
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ175" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS175" t="inlineStr">
@@ -25642,11 +25503,6 @@
       </c>
       <c r="AT175" t="n">
         <v>1</v>
-      </c>
-      <c r="AU175" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
@@ -26319,17 +26175,15 @@
       <c r="O180" t="n">
         <v>0</v>
       </c>
+      <c r="P180" t="n">
+        <v>0</v>
+      </c>
       <c r="Q180" t="n">
         <v>0</v>
       </c>
       <c r="R180" t="n">
         <v>0</v>
       </c>
-      <c r="S180" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U180" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -26337,7 +26191,7 @@
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO180" t="inlineStr">
@@ -26347,12 +26201,7 @@
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ180" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS180" t="inlineStr">
@@ -26362,11 +26211,6 @@
       </c>
       <c r="AT180" t="n">
         <v>1</v>
-      </c>
-      <c r="AU180" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
@@ -26628,17 +26472,15 @@
       <c r="O182" t="n">
         <v>0</v>
       </c>
+      <c r="P182" t="n">
+        <v>0</v>
+      </c>
       <c r="Q182" t="n">
         <v>0</v>
       </c>
       <c r="R182" t="n">
         <v>0</v>
       </c>
-      <c r="S182" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U182" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -26646,7 +26488,7 @@
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO182" t="inlineStr">
@@ -26656,12 +26498,7 @@
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ182" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS182" t="inlineStr">
@@ -26671,11 +26508,6 @@
       </c>
       <c r="AT182" t="n">
         <v>1</v>
-      </c>
-      <c r="AU182" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV182" t="inlineStr">
         <is>
@@ -26937,17 +26769,15 @@
       <c r="O184" t="n">
         <v>0</v>
       </c>
+      <c r="P184" t="n">
+        <v>0</v>
+      </c>
       <c r="Q184" t="n">
         <v>0</v>
       </c>
       <c r="R184" t="n">
         <v>0</v>
       </c>
-      <c r="S184" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U184" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -26955,7 +26785,7 @@
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO184" t="inlineStr">
@@ -26965,12 +26795,7 @@
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ184" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS184" t="inlineStr">
@@ -26980,11 +26805,6 @@
       </c>
       <c r="AT184" t="n">
         <v>1</v>
-      </c>
-      <c r="AU184" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
@@ -27246,17 +27066,15 @@
       <c r="O186" t="n">
         <v>0</v>
       </c>
+      <c r="P186" t="n">
+        <v>0</v>
+      </c>
       <c r="Q186" t="n">
         <v>0</v>
       </c>
       <c r="R186" t="n">
         <v>0</v>
       </c>
-      <c r="S186" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U186" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -27264,7 +27082,7 @@
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO186" t="inlineStr">
@@ -27274,12 +27092,7 @@
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ186" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS186" t="inlineStr">
@@ -27289,11 +27102,6 @@
       </c>
       <c r="AT186" t="n">
         <v>1</v>
-      </c>
-      <c r="AU186" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
@@ -28503,17 +28311,15 @@
       <c r="O194" t="n">
         <v>0</v>
       </c>
+      <c r="P194" t="n">
+        <v>0</v>
+      </c>
       <c r="Q194" t="n">
         <v>0</v>
       </c>
       <c r="R194" t="n">
         <v>0</v>
       </c>
-      <c r="S194" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U194" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -28521,7 +28327,7 @@
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO194" t="inlineStr">
@@ -28531,12 +28337,7 @@
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ194" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS194" t="inlineStr">
@@ -28546,11 +28347,6 @@
       </c>
       <c r="AT194" t="n">
         <v>1</v>
-      </c>
-      <c r="AU194" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV194" t="inlineStr">
         <is>
@@ -28812,17 +28608,15 @@
       <c r="O196" t="n">
         <v>0</v>
       </c>
+      <c r="P196" t="n">
+        <v>0</v>
+      </c>
       <c r="Q196" t="n">
         <v>0</v>
       </c>
       <c r="R196" t="n">
         <v>0</v>
       </c>
-      <c r="S196" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U196" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -28830,7 +28624,7 @@
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO196" t="inlineStr">
@@ -28840,12 +28634,7 @@
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ196" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS196" t="inlineStr">
@@ -28855,11 +28644,6 @@
       </c>
       <c r="AT196" t="n">
         <v>1</v>
-      </c>
-      <c r="AU196" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV196" t="inlineStr">
         <is>
@@ -29121,17 +28905,15 @@
       <c r="O198" t="n">
         <v>0</v>
       </c>
+      <c r="P198" t="n">
+        <v>0</v>
+      </c>
       <c r="Q198" t="n">
         <v>0</v>
       </c>
       <c r="R198" t="n">
         <v>0</v>
       </c>
-      <c r="S198" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U198" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -29139,7 +28921,7 @@
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO198" t="inlineStr">
@@ -29149,12 +28931,7 @@
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ198" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS198" t="inlineStr">
@@ -29164,11 +28941,6 @@
       </c>
       <c r="AT198" t="n">
         <v>1</v>
-      </c>
-      <c r="AU198" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
@@ -29430,17 +29202,15 @@
       <c r="O200" t="n">
         <v>0</v>
       </c>
+      <c r="P200" t="n">
+        <v>0</v>
+      </c>
       <c r="Q200" t="n">
         <v>0</v>
       </c>
       <c r="R200" t="n">
         <v>0</v>
       </c>
-      <c r="S200" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U200" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -29448,7 +29218,7 @@
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO200" t="inlineStr">
@@ -29458,12 +29228,7 @@
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ200" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS200" t="inlineStr">
@@ -29473,11 +29238,6 @@
       </c>
       <c r="AT200" t="n">
         <v>1</v>
-      </c>
-      <c r="AU200" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
@@ -30015,17 +29775,15 @@
       <c r="O204" t="n">
         <v>0</v>
       </c>
+      <c r="P204" t="n">
+        <v>0</v>
+      </c>
       <c r="Q204" t="n">
         <v>0</v>
       </c>
       <c r="R204" t="n">
         <v>0</v>
       </c>
-      <c r="S204" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U204" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -30033,7 +29791,7 @@
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO204" t="inlineStr">
@@ -30043,12 +29801,7 @@
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ204" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS204" t="inlineStr">
@@ -30058,11 +29811,6 @@
       </c>
       <c r="AT204" t="n">
         <v>1</v>
-      </c>
-      <c r="AU204" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
@@ -30459,17 +30207,15 @@
       <c r="O207" t="n">
         <v>0</v>
       </c>
+      <c r="P207" t="n">
+        <v>0</v>
+      </c>
       <c r="Q207" t="n">
         <v>0</v>
       </c>
       <c r="R207" t="n">
         <v>0</v>
       </c>
-      <c r="S207" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U207" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -30477,7 +30223,7 @@
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO207" t="inlineStr">
@@ -30487,12 +30233,7 @@
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ207" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS207" t="inlineStr">
@@ -30502,11 +30243,6 @@
       </c>
       <c r="AT207" t="n">
         <v>1</v>
-      </c>
-      <c r="AU207" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
@@ -30768,17 +30504,15 @@
       <c r="O209" t="n">
         <v>0</v>
       </c>
+      <c r="P209" t="n">
+        <v>0</v>
+      </c>
       <c r="Q209" t="n">
         <v>0</v>
       </c>
       <c r="R209" t="n">
         <v>0</v>
       </c>
-      <c r="S209" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U209" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -30786,7 +30520,7 @@
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO209" t="inlineStr">
@@ -30796,12 +30530,7 @@
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ209" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS209" t="inlineStr">
@@ -30811,11 +30540,6 @@
       </c>
       <c r="AT209" t="n">
         <v>1</v>
-      </c>
-      <c r="AU209" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
@@ -31077,17 +30801,15 @@
       <c r="O211" t="n">
         <v>0</v>
       </c>
+      <c r="P211" t="n">
+        <v>0</v>
+      </c>
       <c r="Q211" t="n">
         <v>0</v>
       </c>
       <c r="R211" t="n">
         <v>0</v>
       </c>
-      <c r="S211" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U211" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -31095,7 +30817,7 @@
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO211" t="inlineStr">
@@ -31105,12 +30827,7 @@
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ211" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS211" t="inlineStr">
@@ -31120,11 +30837,6 @@
       </c>
       <c r="AT211" t="n">
         <v>1</v>
-      </c>
-      <c r="AU211" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
@@ -31662,17 +31374,15 @@
       <c r="O215" t="n">
         <v>0</v>
       </c>
+      <c r="P215" t="n">
+        <v>0</v>
+      </c>
       <c r="Q215" t="n">
         <v>0</v>
       </c>
       <c r="R215" t="n">
         <v>0</v>
       </c>
-      <c r="S215" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U215" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -31680,7 +31390,7 @@
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO215" t="inlineStr">
@@ -31690,12 +31400,7 @@
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ215" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS215" t="inlineStr">
@@ -31705,11 +31410,6 @@
       </c>
       <c r="AT215" t="n">
         <v>1</v>
-      </c>
-      <c r="AU215" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV215" t="inlineStr">
         <is>
@@ -32106,17 +31806,15 @@
       <c r="O218" t="n">
         <v>0</v>
       </c>
+      <c r="P218" t="n">
+        <v>0</v>
+      </c>
       <c r="Q218" t="n">
         <v>0</v>
       </c>
       <c r="R218" t="n">
         <v>0</v>
       </c>
-      <c r="S218" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U218" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -32124,7 +31822,7 @@
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO218" t="inlineStr">
@@ -32134,12 +31832,7 @@
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ218" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS218" t="inlineStr">
@@ -32149,11 +31842,6 @@
       </c>
       <c r="AT218" t="n">
         <v>1</v>
-      </c>
-      <c r="AU218" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV218" t="inlineStr">
         <is>
@@ -32415,17 +32103,15 @@
       <c r="O220" t="n">
         <v>0</v>
       </c>
+      <c r="P220" t="n">
+        <v>0</v>
+      </c>
       <c r="Q220" t="n">
         <v>0</v>
       </c>
       <c r="R220" t="n">
         <v>0</v>
       </c>
-      <c r="S220" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U220" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -32433,7 +32119,7 @@
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO220" t="inlineStr">
@@ -32443,12 +32129,7 @@
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ220" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS220" t="inlineStr">
@@ -32458,11 +32139,6 @@
       </c>
       <c r="AT220" t="n">
         <v>1</v>
-      </c>
-      <c r="AU220" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV220" t="inlineStr">
         <is>
@@ -32724,17 +32400,15 @@
       <c r="O222" t="n">
         <v>0</v>
       </c>
+      <c r="P222" t="n">
+        <v>0</v>
+      </c>
       <c r="Q222" t="n">
         <v>0</v>
       </c>
       <c r="R222" t="n">
         <v>0</v>
       </c>
-      <c r="S222" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U222" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -32742,7 +32416,7 @@
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO222" t="inlineStr">
@@ -32752,12 +32426,7 @@
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ222" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS222" t="inlineStr">
@@ -32767,11 +32436,6 @@
       </c>
       <c r="AT222" t="n">
         <v>1</v>
-      </c>
-      <c r="AU222" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
@@ -33033,17 +32697,15 @@
       <c r="O224" t="n">
         <v>0</v>
       </c>
+      <c r="P224" t="n">
+        <v>0</v>
+      </c>
       <c r="Q224" t="n">
         <v>0</v>
       </c>
       <c r="R224" t="n">
         <v>0</v>
       </c>
-      <c r="S224" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U224" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -33051,7 +32713,7 @@
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO224" t="inlineStr">
@@ -33061,12 +32723,7 @@
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ224" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS224" t="inlineStr">
@@ -33076,11 +32733,6 @@
       </c>
       <c r="AT224" t="n">
         <v>1</v>
-      </c>
-      <c r="AU224" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
@@ -33753,17 +33405,15 @@
       <c r="O229" t="n">
         <v>0</v>
       </c>
+      <c r="P229" t="n">
+        <v>0</v>
+      </c>
       <c r="Q229" t="n">
         <v>0</v>
       </c>
       <c r="R229" t="n">
         <v>0</v>
       </c>
-      <c r="S229" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U229" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -33771,7 +33421,7 @@
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO229" t="inlineStr">
@@ -33781,12 +33431,7 @@
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ229" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS229" t="inlineStr">
@@ -33796,11 +33441,6 @@
       </c>
       <c r="AT229" t="n">
         <v>1</v>
-      </c>
-      <c r="AU229" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV229" t="inlineStr">
         <is>
@@ -34062,17 +33702,15 @@
       <c r="O231" t="n">
         <v>0</v>
       </c>
+      <c r="P231" t="n">
+        <v>0</v>
+      </c>
       <c r="Q231" t="n">
         <v>0</v>
       </c>
       <c r="R231" t="n">
         <v>0</v>
       </c>
-      <c r="S231" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U231" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -34080,7 +33718,7 @@
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO231" t="inlineStr">
@@ -34090,12 +33728,7 @@
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ231" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS231" t="inlineStr">
@@ -34105,11 +33738,6 @@
       </c>
       <c r="AT231" t="n">
         <v>1</v>
-      </c>
-      <c r="AU231" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
@@ -34371,17 +33999,15 @@
       <c r="O233" t="n">
         <v>0</v>
       </c>
+      <c r="P233" t="n">
+        <v>0</v>
+      </c>
       <c r="Q233" t="n">
         <v>0</v>
       </c>
       <c r="R233" t="n">
         <v>0</v>
       </c>
-      <c r="S233" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U233" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -34389,7 +34015,7 @@
       </c>
       <c r="AA233" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO233" t="inlineStr">
@@ -34399,12 +34025,7 @@
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ233" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS233" t="inlineStr">
@@ -34414,11 +34035,6 @@
       </c>
       <c r="AT233" t="n">
         <v>1</v>
-      </c>
-      <c r="AU233" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
@@ -34680,17 +34296,15 @@
       <c r="O235" t="n">
         <v>0</v>
       </c>
+      <c r="P235" t="n">
+        <v>0</v>
+      </c>
       <c r="Q235" t="n">
         <v>0</v>
       </c>
       <c r="R235" t="n">
         <v>0</v>
       </c>
-      <c r="S235" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U235" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -34698,7 +34312,7 @@
       </c>
       <c r="AA235" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO235" t="inlineStr">
@@ -34708,12 +34322,7 @@
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ235" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS235" t="inlineStr">
@@ -34723,11 +34332,6 @@
       </c>
       <c r="AT235" t="n">
         <v>1</v>
-      </c>
-      <c r="AU235" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV235" t="inlineStr">
         <is>
@@ -35400,17 +35004,15 @@
       <c r="O240" t="n">
         <v>0</v>
       </c>
+      <c r="P240" t="n">
+        <v>0</v>
+      </c>
       <c r="Q240" t="n">
         <v>0</v>
       </c>
       <c r="R240" t="n">
         <v>0</v>
       </c>
-      <c r="S240" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U240" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -35418,7 +35020,7 @@
       </c>
       <c r="AA240" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO240" t="inlineStr">
@@ -35428,12 +35030,7 @@
       </c>
       <c r="AP240" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ240" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS240" t="inlineStr">
@@ -35443,11 +35040,6 @@
       </c>
       <c r="AT240" t="n">
         <v>1</v>
-      </c>
-      <c r="AU240" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV240" t="inlineStr">
         <is>
@@ -35709,17 +35301,15 @@
       <c r="O242" t="n">
         <v>0</v>
       </c>
+      <c r="P242" t="n">
+        <v>0</v>
+      </c>
       <c r="Q242" t="n">
         <v>0</v>
       </c>
       <c r="R242" t="n">
         <v>0</v>
       </c>
-      <c r="S242" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U242" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -35727,7 +35317,7 @@
       </c>
       <c r="AA242" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO242" t="inlineStr">
@@ -35737,12 +35327,7 @@
       </c>
       <c r="AP242" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ242" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS242" t="inlineStr">
@@ -35752,11 +35337,6 @@
       </c>
       <c r="AT242" t="n">
         <v>1</v>
-      </c>
-      <c r="AU242" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV242" t="inlineStr">
         <is>
@@ -36018,17 +35598,15 @@
       <c r="O244" t="n">
         <v>0</v>
       </c>
+      <c r="P244" t="n">
+        <v>0</v>
+      </c>
       <c r="Q244" t="n">
         <v>0</v>
       </c>
       <c r="R244" t="n">
         <v>0</v>
       </c>
-      <c r="S244" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U244" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -36036,7 +35614,7 @@
       </c>
       <c r="AA244" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO244" t="inlineStr">
@@ -36046,12 +35624,7 @@
       </c>
       <c r="AP244" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ244" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS244" t="inlineStr">
@@ -36061,11 +35634,6 @@
       </c>
       <c r="AT244" t="n">
         <v>1</v>
-      </c>
-      <c r="AU244" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV244" t="inlineStr">
         <is>
@@ -36327,17 +35895,15 @@
       <c r="O246" t="n">
         <v>0</v>
       </c>
+      <c r="P246" t="n">
+        <v>0</v>
+      </c>
       <c r="Q246" t="n">
         <v>0</v>
       </c>
       <c r="R246" t="n">
         <v>0</v>
       </c>
-      <c r="S246" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U246" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -36345,7 +35911,7 @@
       </c>
       <c r="AA246" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO246" t="inlineStr">
@@ -36355,12 +35921,7 @@
       </c>
       <c r="AP246" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ246" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS246" t="inlineStr">
@@ -36370,11 +35931,6 @@
       </c>
       <c r="AT246" t="n">
         <v>1</v>
-      </c>
-      <c r="AU246" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV246" t="inlineStr">
         <is>
@@ -36636,17 +36192,15 @@
       <c r="O248" t="n">
         <v>0</v>
       </c>
+      <c r="P248" t="n">
+        <v>0</v>
+      </c>
       <c r="Q248" t="n">
         <v>0</v>
       </c>
       <c r="R248" t="n">
         <v>0</v>
       </c>
-      <c r="S248" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U248" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -36654,7 +36208,7 @@
       </c>
       <c r="AA248" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO248" t="inlineStr">
@@ -36664,12 +36218,7 @@
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ248" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS248" t="inlineStr">
@@ -36679,11 +36228,6 @@
       </c>
       <c r="AT248" t="n">
         <v>1</v>
-      </c>
-      <c r="AU248" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
@@ -37356,17 +36900,15 @@
       <c r="O253" t="n">
         <v>0</v>
       </c>
+      <c r="P253" t="n">
+        <v>0</v>
+      </c>
       <c r="Q253" t="n">
         <v>0</v>
       </c>
       <c r="R253" t="n">
         <v>0</v>
       </c>
-      <c r="S253" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U253" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -37374,7 +36916,7 @@
       </c>
       <c r="AA253" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO253" t="inlineStr">
@@ -37384,12 +36926,7 @@
       </c>
       <c r="AP253" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ253" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS253" t="inlineStr">
@@ -37399,11 +36936,6 @@
       </c>
       <c r="AT253" t="n">
         <v>1</v>
-      </c>
-      <c r="AU253" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV253" t="inlineStr">
         <is>
@@ -37665,17 +37197,15 @@
       <c r="O255" t="n">
         <v>0</v>
       </c>
+      <c r="P255" t="n">
+        <v>0</v>
+      </c>
       <c r="Q255" t="n">
         <v>0</v>
       </c>
       <c r="R255" t="n">
         <v>0</v>
       </c>
-      <c r="S255" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U255" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -37683,7 +37213,7 @@
       </c>
       <c r="AA255" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO255" t="inlineStr">
@@ -37693,12 +37223,7 @@
       </c>
       <c r="AP255" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ255" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS255" t="inlineStr">
@@ -37708,11 +37233,6 @@
       </c>
       <c r="AT255" t="n">
         <v>1</v>
-      </c>
-      <c r="AU255" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV255" t="inlineStr">
         <is>
@@ -37974,17 +37494,15 @@
       <c r="O257" t="n">
         <v>0</v>
       </c>
+      <c r="P257" t="n">
+        <v>0</v>
+      </c>
       <c r="Q257" t="n">
         <v>0</v>
       </c>
       <c r="R257" t="n">
         <v>0</v>
       </c>
-      <c r="S257" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U257" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -37992,7 +37510,7 @@
       </c>
       <c r="AA257" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO257" t="inlineStr">
@@ -38002,12 +37520,7 @@
       </c>
       <c r="AP257" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ257" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS257" t="inlineStr">
@@ -38017,11 +37530,6 @@
       </c>
       <c r="AT257" t="n">
         <v>1</v>
-      </c>
-      <c r="AU257" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV257" t="inlineStr">
         <is>
@@ -38283,17 +37791,15 @@
       <c r="O259" t="n">
         <v>0</v>
       </c>
+      <c r="P259" t="n">
+        <v>0</v>
+      </c>
       <c r="Q259" t="n">
         <v>0</v>
       </c>
       <c r="R259" t="n">
         <v>0</v>
       </c>
-      <c r="S259" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U259" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -38301,7 +37807,7 @@
       </c>
       <c r="AA259" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO259" t="inlineStr">
@@ -38311,12 +37817,7 @@
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ259" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS259" t="inlineStr">
@@ -38326,11 +37827,6 @@
       </c>
       <c r="AT259" t="n">
         <v>1</v>
-      </c>
-      <c r="AU259" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV259" t="inlineStr">
         <is>
@@ -39003,17 +38499,15 @@
       <c r="O264" t="n">
         <v>0</v>
       </c>
+      <c r="P264" t="n">
+        <v>0</v>
+      </c>
       <c r="Q264" t="n">
         <v>0</v>
       </c>
       <c r="R264" t="n">
         <v>0</v>
       </c>
-      <c r="S264" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U264" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -39021,7 +38515,7 @@
       </c>
       <c r="AA264" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO264" t="inlineStr">
@@ -39031,12 +38525,7 @@
       </c>
       <c r="AP264" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ264" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS264" t="inlineStr">
@@ -39046,11 +38535,6 @@
       </c>
       <c r="AT264" t="n">
         <v>1</v>
-      </c>
-      <c r="AU264" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV264" t="inlineStr">
         <is>
@@ -39312,17 +38796,15 @@
       <c r="O266" t="n">
         <v>0</v>
       </c>
+      <c r="P266" t="n">
+        <v>0</v>
+      </c>
       <c r="Q266" t="n">
         <v>0</v>
       </c>
       <c r="R266" t="n">
         <v>0</v>
       </c>
-      <c r="S266" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U266" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -39330,7 +38812,7 @@
       </c>
       <c r="AA266" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO266" t="inlineStr">
@@ -39340,12 +38822,7 @@
       </c>
       <c r="AP266" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ266" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS266" t="inlineStr">
@@ -39355,11 +38832,6 @@
       </c>
       <c r="AT266" t="n">
         <v>1</v>
-      </c>
-      <c r="AU266" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV266" t="inlineStr">
         <is>
@@ -39621,17 +39093,15 @@
       <c r="O268" t="n">
         <v>0</v>
       </c>
+      <c r="P268" t="n">
+        <v>0</v>
+      </c>
       <c r="Q268" t="n">
         <v>0</v>
       </c>
       <c r="R268" t="n">
         <v>0</v>
       </c>
-      <c r="S268" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U268" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -39639,7 +39109,7 @@
       </c>
       <c r="AA268" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO268" t="inlineStr">
@@ -39649,12 +39119,7 @@
       </c>
       <c r="AP268" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ268" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS268" t="inlineStr">
@@ -39664,11 +39129,6 @@
       </c>
       <c r="AT268" t="n">
         <v>1</v>
-      </c>
-      <c r="AU268" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV268" t="inlineStr">
         <is>
@@ -39930,17 +39390,15 @@
       <c r="O270" t="n">
         <v>0</v>
       </c>
+      <c r="P270" t="n">
+        <v>0</v>
+      </c>
       <c r="Q270" t="n">
         <v>0</v>
       </c>
       <c r="R270" t="n">
         <v>0</v>
       </c>
-      <c r="S270" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U270" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -39948,7 +39406,7 @@
       </c>
       <c r="AA270" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO270" t="inlineStr">
@@ -39958,12 +39416,7 @@
       </c>
       <c r="AP270" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ270" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS270" t="inlineStr">
@@ -39973,11 +39426,6 @@
       </c>
       <c r="AT270" t="n">
         <v>1</v>
-      </c>
-      <c r="AU270" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV270" t="inlineStr">
         <is>
@@ -40650,17 +40098,15 @@
       <c r="O275" t="n">
         <v>0</v>
       </c>
+      <c r="P275" t="n">
+        <v>0</v>
+      </c>
       <c r="Q275" t="n">
         <v>0</v>
       </c>
       <c r="R275" t="n">
         <v>0</v>
       </c>
-      <c r="S275" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U275" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -40668,7 +40114,7 @@
       </c>
       <c r="AA275" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO275" t="inlineStr">
@@ -40678,12 +40124,7 @@
       </c>
       <c r="AP275" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ275" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS275" t="inlineStr">
@@ -40693,11 +40134,6 @@
       </c>
       <c r="AT275" t="n">
         <v>1</v>
-      </c>
-      <c r="AU275" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV275" t="inlineStr">
         <is>
@@ -40959,17 +40395,15 @@
       <c r="O277" t="n">
         <v>0</v>
       </c>
+      <c r="P277" t="n">
+        <v>0</v>
+      </c>
       <c r="Q277" t="n">
         <v>0</v>
       </c>
       <c r="R277" t="n">
         <v>0</v>
       </c>
-      <c r="S277" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U277" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -40977,7 +40411,7 @@
       </c>
       <c r="AA277" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO277" t="inlineStr">
@@ -40987,12 +40421,7 @@
       </c>
       <c r="AP277" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ277" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS277" t="inlineStr">
@@ -41002,11 +40431,6 @@
       </c>
       <c r="AT277" t="n">
         <v>1</v>
-      </c>
-      <c r="AU277" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV277" t="inlineStr">
         <is>
@@ -41268,17 +40692,15 @@
       <c r="O279" t="n">
         <v>0</v>
       </c>
+      <c r="P279" t="n">
+        <v>0</v>
+      </c>
       <c r="Q279" t="n">
         <v>0</v>
       </c>
       <c r="R279" t="n">
         <v>0</v>
       </c>
-      <c r="S279" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U279" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -41286,7 +40708,7 @@
       </c>
       <c r="AA279" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO279" t="inlineStr">
@@ -41296,12 +40718,7 @@
       </c>
       <c r="AP279" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ279" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS279" t="inlineStr">
@@ -41311,11 +40728,6 @@
       </c>
       <c r="AT279" t="n">
         <v>1</v>
-      </c>
-      <c r="AU279" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV279" t="inlineStr">
         <is>
@@ -41577,17 +40989,15 @@
       <c r="O281" t="n">
         <v>0</v>
       </c>
+      <c r="P281" t="n">
+        <v>0</v>
+      </c>
       <c r="Q281" t="n">
         <v>0</v>
       </c>
       <c r="R281" t="n">
         <v>0</v>
       </c>
-      <c r="S281" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U281" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -41595,7 +41005,7 @@
       </c>
       <c r="AA281" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO281" t="inlineStr">
@@ -41605,12 +41015,7 @@
       </c>
       <c r="AP281" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ281" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS281" t="inlineStr">
@@ -41620,11 +41025,6 @@
       </c>
       <c r="AT281" t="n">
         <v>1</v>
-      </c>
-      <c r="AU281" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV281" t="inlineStr">
         <is>
@@ -41886,17 +41286,15 @@
       <c r="O283" t="n">
         <v>0</v>
       </c>
+      <c r="P283" t="n">
+        <v>0</v>
+      </c>
       <c r="Q283" t="n">
         <v>0</v>
       </c>
       <c r="R283" t="n">
         <v>0</v>
       </c>
-      <c r="S283" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U283" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -41904,7 +41302,7 @@
       </c>
       <c r="AA283" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO283" t="inlineStr">
@@ -41914,12 +41312,7 @@
       </c>
       <c r="AP283" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ283" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS283" t="inlineStr">
@@ -41929,11 +41322,6 @@
       </c>
       <c r="AT283" t="n">
         <v>1</v>
-      </c>
-      <c r="AU283" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV283" t="inlineStr">
         <is>
@@ -42606,17 +41994,15 @@
       <c r="O288" t="n">
         <v>0</v>
       </c>
+      <c r="P288" t="n">
+        <v>0</v>
+      </c>
       <c r="Q288" t="n">
         <v>0</v>
       </c>
       <c r="R288" t="n">
         <v>0</v>
       </c>
-      <c r="S288" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U288" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -42624,7 +42010,7 @@
       </c>
       <c r="AA288" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO288" t="inlineStr">
@@ -42634,12 +42020,7 @@
       </c>
       <c r="AP288" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ288" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS288" t="inlineStr">
@@ -42649,11 +42030,6 @@
       </c>
       <c r="AT288" t="n">
         <v>1</v>
-      </c>
-      <c r="AU288" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV288" t="inlineStr">
         <is>
@@ -42915,17 +42291,15 @@
       <c r="O290" t="n">
         <v>0</v>
       </c>
+      <c r="P290" t="n">
+        <v>0</v>
+      </c>
       <c r="Q290" t="n">
         <v>0</v>
       </c>
       <c r="R290" t="n">
         <v>0</v>
       </c>
-      <c r="S290" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U290" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -42933,7 +42307,7 @@
       </c>
       <c r="AA290" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO290" t="inlineStr">
@@ -42943,12 +42317,7 @@
       </c>
       <c r="AP290" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ290" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS290" t="inlineStr">
@@ -42958,11 +42327,6 @@
       </c>
       <c r="AT290" t="n">
         <v>1</v>
-      </c>
-      <c r="AU290" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV290" t="inlineStr">
         <is>
@@ -43224,17 +42588,15 @@
       <c r="O292" t="n">
         <v>0</v>
       </c>
+      <c r="P292" t="n">
+        <v>0</v>
+      </c>
       <c r="Q292" t="n">
         <v>0</v>
       </c>
       <c r="R292" t="n">
         <v>0</v>
       </c>
-      <c r="S292" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U292" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -43242,7 +42604,7 @@
       </c>
       <c r="AA292" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO292" t="inlineStr">
@@ -43252,12 +42614,7 @@
       </c>
       <c r="AP292" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ292" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS292" t="inlineStr">
@@ -43267,11 +42624,6 @@
       </c>
       <c r="AT292" t="n">
         <v>1</v>
-      </c>
-      <c r="AU292" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV292" t="inlineStr">
         <is>
@@ -43533,17 +42885,15 @@
       <c r="O294" t="n">
         <v>0</v>
       </c>
+      <c r="P294" t="n">
+        <v>0</v>
+      </c>
       <c r="Q294" t="n">
         <v>0</v>
       </c>
       <c r="R294" t="n">
         <v>0</v>
       </c>
-      <c r="S294" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U294" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -43551,7 +42901,7 @@
       </c>
       <c r="AA294" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO294" t="inlineStr">
@@ -43561,12 +42911,7 @@
       </c>
       <c r="AP294" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ294" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS294" t="inlineStr">
@@ -43576,11 +42921,6 @@
       </c>
       <c r="AT294" t="n">
         <v>1</v>
-      </c>
-      <c r="AU294" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV294" t="inlineStr">
         <is>
@@ -44253,17 +43593,15 @@
       <c r="O299" t="n">
         <v>0</v>
       </c>
+      <c r="P299" t="n">
+        <v>0</v>
+      </c>
       <c r="Q299" t="n">
         <v>0</v>
       </c>
       <c r="R299" t="n">
         <v>0</v>
       </c>
-      <c r="S299" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U299" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -44271,7 +43609,7 @@
       </c>
       <c r="AA299" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO299" t="inlineStr">
@@ -44281,12 +43619,7 @@
       </c>
       <c r="AP299" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ299" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS299" t="inlineStr">
@@ -44296,11 +43629,6 @@
       </c>
       <c r="AT299" t="n">
         <v>1</v>
-      </c>
-      <c r="AU299" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV299" t="inlineStr">
         <is>
@@ -44562,17 +43890,15 @@
       <c r="O301" t="n">
         <v>0</v>
       </c>
+      <c r="P301" t="n">
+        <v>0</v>
+      </c>
       <c r="Q301" t="n">
         <v>0</v>
       </c>
       <c r="R301" t="n">
         <v>0</v>
       </c>
-      <c r="S301" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U301" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -44580,7 +43906,7 @@
       </c>
       <c r="AA301" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO301" t="inlineStr">
@@ -44590,12 +43916,7 @@
       </c>
       <c r="AP301" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ301" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS301" t="inlineStr">
@@ -44605,11 +43926,6 @@
       </c>
       <c r="AT301" t="n">
         <v>1</v>
-      </c>
-      <c r="AU301" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV301" t="inlineStr">
         <is>
@@ -44871,17 +44187,15 @@
       <c r="O303" t="n">
         <v>0</v>
       </c>
+      <c r="P303" t="n">
+        <v>0</v>
+      </c>
       <c r="Q303" t="n">
         <v>0</v>
       </c>
       <c r="R303" t="n">
         <v>0</v>
       </c>
-      <c r="S303" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U303" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -44889,7 +44203,7 @@
       </c>
       <c r="AA303" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO303" t="inlineStr">
@@ -44899,12 +44213,7 @@
       </c>
       <c r="AP303" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ303" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS303" t="inlineStr">
@@ -44914,11 +44223,6 @@
       </c>
       <c r="AT303" t="n">
         <v>1</v>
-      </c>
-      <c r="AU303" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV303" t="inlineStr">
         <is>
@@ -45180,17 +44484,15 @@
       <c r="O305" t="n">
         <v>0</v>
       </c>
+      <c r="P305" t="n">
+        <v>0</v>
+      </c>
       <c r="Q305" t="n">
         <v>0</v>
       </c>
       <c r="R305" t="n">
         <v>0</v>
       </c>
-      <c r="S305" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U305" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -45198,7 +44500,7 @@
       </c>
       <c r="AA305" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO305" t="inlineStr">
@@ -45208,12 +44510,7 @@
       </c>
       <c r="AP305" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ305" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS305" t="inlineStr">
@@ -45223,11 +44520,6 @@
       </c>
       <c r="AT305" t="n">
         <v>1</v>
-      </c>
-      <c r="AU305" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV305" t="inlineStr">
         <is>
@@ -45765,17 +45057,15 @@
       <c r="O309" t="n">
         <v>0</v>
       </c>
+      <c r="P309" t="n">
+        <v>0</v>
+      </c>
       <c r="Q309" t="n">
         <v>0</v>
       </c>
       <c r="R309" t="n">
         <v>0</v>
       </c>
-      <c r="S309" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U309" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -45783,7 +45073,7 @@
       </c>
       <c r="AA309" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO309" t="inlineStr">
@@ -45793,12 +45083,7 @@
       </c>
       <c r="AP309" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ309" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS309" t="inlineStr">
@@ -45808,11 +45093,6 @@
       </c>
       <c r="AT309" t="n">
         <v>1</v>
-      </c>
-      <c r="AU309" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV309" t="inlineStr">
         <is>
@@ -46209,17 +45489,15 @@
       <c r="O312" t="n">
         <v>0</v>
       </c>
+      <c r="P312" t="n">
+        <v>0</v>
+      </c>
       <c r="Q312" t="n">
         <v>0</v>
       </c>
       <c r="R312" t="n">
         <v>0</v>
       </c>
-      <c r="S312" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U312" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -46227,7 +45505,7 @@
       </c>
       <c r="AA312" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO312" t="inlineStr">
@@ -46237,12 +45515,7 @@
       </c>
       <c r="AP312" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ312" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS312" t="inlineStr">
@@ -46252,11 +45525,6 @@
       </c>
       <c r="AT312" t="n">
         <v>1</v>
-      </c>
-      <c r="AU312" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV312" t="inlineStr">
         <is>
@@ -46518,17 +45786,15 @@
       <c r="O314" t="n">
         <v>0</v>
       </c>
+      <c r="P314" t="n">
+        <v>0</v>
+      </c>
       <c r="Q314" t="n">
         <v>0</v>
       </c>
       <c r="R314" t="n">
         <v>0</v>
       </c>
-      <c r="S314" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U314" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -46536,7 +45802,7 @@
       </c>
       <c r="AA314" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO314" t="inlineStr">
@@ -46546,12 +45812,7 @@
       </c>
       <c r="AP314" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ314" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS314" t="inlineStr">
@@ -46561,11 +45822,6 @@
       </c>
       <c r="AT314" t="n">
         <v>1</v>
-      </c>
-      <c r="AU314" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV314" t="inlineStr">
         <is>
@@ -46827,17 +46083,15 @@
       <c r="O316" t="n">
         <v>0</v>
       </c>
+      <c r="P316" t="n">
+        <v>0</v>
+      </c>
       <c r="Q316" t="n">
         <v>0</v>
       </c>
       <c r="R316" t="n">
         <v>0</v>
       </c>
-      <c r="S316" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U316" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -46845,7 +46099,7 @@
       </c>
       <c r="AA316" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO316" t="inlineStr">
@@ -46855,12 +46109,7 @@
       </c>
       <c r="AP316" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ316" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS316" t="inlineStr">
@@ -46870,11 +46119,6 @@
       </c>
       <c r="AT316" t="n">
         <v>1</v>
-      </c>
-      <c r="AU316" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV316" t="inlineStr">
         <is>
@@ -47136,17 +46380,15 @@
       <c r="O318" t="n">
         <v>0</v>
       </c>
+      <c r="P318" t="n">
+        <v>0</v>
+      </c>
       <c r="Q318" t="n">
         <v>0</v>
       </c>
       <c r="R318" t="n">
         <v>0</v>
       </c>
-      <c r="S318" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U318" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -47154,7 +46396,7 @@
       </c>
       <c r="AA318" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO318" t="inlineStr">
@@ -47164,12 +46406,7 @@
       </c>
       <c r="AP318" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ318" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS318" t="inlineStr">
@@ -47179,11 +46416,6 @@
       </c>
       <c r="AT318" t="n">
         <v>1</v>
-      </c>
-      <c r="AU318" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV318" t="inlineStr">
         <is>
@@ -47856,17 +47088,15 @@
       <c r="O323" t="n">
         <v>0</v>
       </c>
+      <c r="P323" t="n">
+        <v>0</v>
+      </c>
       <c r="Q323" t="n">
         <v>0</v>
       </c>
       <c r="R323" t="n">
         <v>0</v>
       </c>
-      <c r="S323" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U323" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -47874,7 +47104,7 @@
       </c>
       <c r="AA323" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO323" t="inlineStr">
@@ -47884,12 +47114,7 @@
       </c>
       <c r="AP323" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ323" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS323" t="inlineStr">
@@ -47899,11 +47124,6 @@
       </c>
       <c r="AT323" t="n">
         <v>1</v>
-      </c>
-      <c r="AU323" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV323" t="inlineStr">
         <is>
@@ -48165,17 +47385,15 @@
       <c r="O325" t="n">
         <v>0</v>
       </c>
+      <c r="P325" t="n">
+        <v>0</v>
+      </c>
       <c r="Q325" t="n">
         <v>0</v>
       </c>
       <c r="R325" t="n">
         <v>0</v>
       </c>
-      <c r="S325" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U325" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -48183,7 +47401,7 @@
       </c>
       <c r="AA325" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO325" t="inlineStr">
@@ -48193,12 +47411,7 @@
       </c>
       <c r="AP325" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ325" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS325" t="inlineStr">
@@ -48208,11 +47421,6 @@
       </c>
       <c r="AT325" t="n">
         <v>1</v>
-      </c>
-      <c r="AU325" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV325" t="inlineStr">
         <is>
@@ -48474,17 +47682,15 @@
       <c r="O327" t="n">
         <v>0</v>
       </c>
+      <c r="P327" t="n">
+        <v>0</v>
+      </c>
       <c r="Q327" t="n">
         <v>0</v>
       </c>
       <c r="R327" t="n">
         <v>0</v>
       </c>
-      <c r="S327" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U327" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -48492,7 +47698,7 @@
       </c>
       <c r="AA327" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO327" t="inlineStr">
@@ -48502,12 +47708,7 @@
       </c>
       <c r="AP327" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ327" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS327" t="inlineStr">
@@ -48517,11 +47718,6 @@
       </c>
       <c r="AT327" t="n">
         <v>1</v>
-      </c>
-      <c r="AU327" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV327" t="inlineStr">
         <is>
@@ -48783,17 +47979,15 @@
       <c r="O329" t="n">
         <v>0</v>
       </c>
+      <c r="P329" t="n">
+        <v>0</v>
+      </c>
       <c r="Q329" t="n">
         <v>0</v>
       </c>
       <c r="R329" t="n">
         <v>0</v>
       </c>
-      <c r="S329" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U329" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -48801,7 +47995,7 @@
       </c>
       <c r="AA329" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO329" t="inlineStr">
@@ -48811,12 +48005,7 @@
       </c>
       <c r="AP329" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ329" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS329" t="inlineStr">
@@ -48826,11 +48015,6 @@
       </c>
       <c r="AT329" t="n">
         <v>1</v>
-      </c>
-      <c r="AU329" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV329" t="inlineStr">
         <is>
@@ -50040,17 +49224,15 @@
       <c r="O337" t="n">
         <v>0</v>
       </c>
+      <c r="P337" t="n">
+        <v>0</v>
+      </c>
       <c r="Q337" t="n">
         <v>0</v>
       </c>
       <c r="R337" t="n">
         <v>0</v>
       </c>
-      <c r="S337" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U337" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -50058,7 +49240,7 @@
       </c>
       <c r="AA337" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO337" t="inlineStr">
@@ -50068,12 +49250,7 @@
       </c>
       <c r="AP337" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ337" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS337" t="inlineStr">
@@ -50083,11 +49260,6 @@
       </c>
       <c r="AT337" t="n">
         <v>1</v>
-      </c>
-      <c r="AU337" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV337" t="inlineStr">
         <is>
@@ -50349,17 +49521,15 @@
       <c r="O339" t="n">
         <v>0</v>
       </c>
+      <c r="P339" t="n">
+        <v>0</v>
+      </c>
       <c r="Q339" t="n">
         <v>0</v>
       </c>
       <c r="R339" t="n">
         <v>0</v>
       </c>
-      <c r="S339" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U339" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -50367,7 +49537,7 @@
       </c>
       <c r="AA339" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO339" t="inlineStr">
@@ -50377,12 +49547,7 @@
       </c>
       <c r="AP339" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ339" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS339" t="inlineStr">
@@ -50392,11 +49557,6 @@
       </c>
       <c r="AT339" t="n">
         <v>1</v>
-      </c>
-      <c r="AU339" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV339" t="inlineStr">
         <is>
@@ -50658,17 +49818,15 @@
       <c r="O341" t="n">
         <v>0</v>
       </c>
+      <c r="P341" t="n">
+        <v>0</v>
+      </c>
       <c r="Q341" t="n">
         <v>0</v>
       </c>
       <c r="R341" t="n">
         <v>0</v>
       </c>
-      <c r="S341" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U341" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -50676,7 +49834,7 @@
       </c>
       <c r="AA341" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO341" t="inlineStr">
@@ -50686,12 +49844,7 @@
       </c>
       <c r="AP341" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ341" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS341" t="inlineStr">
@@ -50701,11 +49854,6 @@
       </c>
       <c r="AT341" t="n">
         <v>1</v>
-      </c>
-      <c r="AU341" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV341" t="inlineStr">
         <is>
@@ -50967,17 +50115,15 @@
       <c r="O343" t="n">
         <v>0</v>
       </c>
+      <c r="P343" t="n">
+        <v>0</v>
+      </c>
       <c r="Q343" t="n">
         <v>0</v>
       </c>
       <c r="R343" t="n">
         <v>0</v>
       </c>
-      <c r="S343" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U343" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -50985,7 +50131,7 @@
       </c>
       <c r="AA343" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO343" t="inlineStr">
@@ -50995,12 +50141,7 @@
       </c>
       <c r="AP343" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ343" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS343" t="inlineStr">
@@ -51010,11 +50151,6 @@
       </c>
       <c r="AT343" t="n">
         <v>1</v>
-      </c>
-      <c r="AU343" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV343" t="inlineStr">
         <is>
@@ -51276,17 +50412,15 @@
       <c r="O345" t="n">
         <v>0</v>
       </c>
+      <c r="P345" t="n">
+        <v>0</v>
+      </c>
       <c r="Q345" t="n">
         <v>0</v>
       </c>
       <c r="R345" t="n">
         <v>0</v>
       </c>
-      <c r="S345" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U345" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -51294,7 +50428,7 @@
       </c>
       <c r="AA345" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO345" t="inlineStr">
@@ -51304,12 +50438,7 @@
       </c>
       <c r="AP345" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ345" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS345" t="inlineStr">
@@ -51319,11 +50448,6 @@
       </c>
       <c r="AT345" t="n">
         <v>1</v>
-      </c>
-      <c r="AU345" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV345" t="inlineStr">
         <is>
@@ -51996,17 +51120,15 @@
       <c r="O350" t="n">
         <v>0</v>
       </c>
+      <c r="P350" t="n">
+        <v>0</v>
+      </c>
       <c r="Q350" t="n">
         <v>0</v>
       </c>
       <c r="R350" t="n">
         <v>0</v>
       </c>
-      <c r="S350" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U350" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -52014,7 +51136,7 @@
       </c>
       <c r="AA350" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO350" t="inlineStr">
@@ -52024,12 +51146,7 @@
       </c>
       <c r="AP350" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ350" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS350" t="inlineStr">
@@ -52039,11 +51156,6 @@
       </c>
       <c r="AT350" t="n">
         <v>1</v>
-      </c>
-      <c r="AU350" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV350" t="inlineStr">
         <is>
@@ -52305,17 +51417,15 @@
       <c r="O352" t="n">
         <v>0</v>
       </c>
+      <c r="P352" t="n">
+        <v>0</v>
+      </c>
       <c r="Q352" t="n">
         <v>0</v>
       </c>
       <c r="R352" t="n">
         <v>0</v>
       </c>
-      <c r="S352" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U352" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -52323,7 +51433,7 @@
       </c>
       <c r="AA352" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO352" t="inlineStr">
@@ -52333,12 +51443,7 @@
       </c>
       <c r="AP352" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ352" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS352" t="inlineStr">
@@ -52348,11 +51453,6 @@
       </c>
       <c r="AT352" t="n">
         <v>1</v>
-      </c>
-      <c r="AU352" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV352" t="inlineStr">
         <is>
@@ -52614,17 +51714,15 @@
       <c r="O354" t="n">
         <v>0</v>
       </c>
+      <c r="P354" t="n">
+        <v>0</v>
+      </c>
       <c r="Q354" t="n">
         <v>0</v>
       </c>
       <c r="R354" t="n">
         <v>0</v>
       </c>
-      <c r="S354" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U354" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -52632,7 +51730,7 @@
       </c>
       <c r="AA354" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO354" t="inlineStr">
@@ -52642,12 +51740,7 @@
       </c>
       <c r="AP354" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ354" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS354" t="inlineStr">
@@ -52657,11 +51750,6 @@
       </c>
       <c r="AT354" t="n">
         <v>1</v>
-      </c>
-      <c r="AU354" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV354" t="inlineStr">
         <is>
@@ -52923,17 +52011,15 @@
       <c r="O356" t="n">
         <v>0</v>
       </c>
+      <c r="P356" t="n">
+        <v>0</v>
+      </c>
       <c r="Q356" t="n">
         <v>0</v>
       </c>
       <c r="R356" t="n">
         <v>0</v>
       </c>
-      <c r="S356" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U356" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -52941,7 +52027,7 @@
       </c>
       <c r="AA356" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO356" t="inlineStr">
@@ -52951,12 +52037,7 @@
       </c>
       <c r="AP356" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ356" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS356" t="inlineStr">
@@ -52966,11 +52047,6 @@
       </c>
       <c r="AT356" t="n">
         <v>1</v>
-      </c>
-      <c r="AU356" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV356" t="inlineStr">
         <is>
@@ -53643,17 +52719,15 @@
       <c r="O361" t="n">
         <v>0</v>
       </c>
+      <c r="P361" t="n">
+        <v>0</v>
+      </c>
       <c r="Q361" t="n">
         <v>0</v>
       </c>
       <c r="R361" t="n">
         <v>0</v>
       </c>
-      <c r="S361" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U361" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -53661,7 +52735,7 @@
       </c>
       <c r="AA361" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO361" t="inlineStr">
@@ -53671,12 +52745,7 @@
       </c>
       <c r="AP361" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ361" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS361" t="inlineStr">
@@ -53686,11 +52755,6 @@
       </c>
       <c r="AT361" t="n">
         <v>1</v>
-      </c>
-      <c r="AU361" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV361" t="inlineStr">
         <is>
@@ -53952,17 +53016,15 @@
       <c r="O363" t="n">
         <v>0</v>
       </c>
+      <c r="P363" t="n">
+        <v>0</v>
+      </c>
       <c r="Q363" t="n">
         <v>0</v>
       </c>
       <c r="R363" t="n">
         <v>0</v>
       </c>
-      <c r="S363" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U363" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -53970,7 +53032,7 @@
       </c>
       <c r="AA363" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO363" t="inlineStr">
@@ -53980,12 +53042,7 @@
       </c>
       <c r="AP363" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ363" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS363" t="inlineStr">
@@ -53995,11 +53052,6 @@
       </c>
       <c r="AT363" t="n">
         <v>1</v>
-      </c>
-      <c r="AU363" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV363" t="inlineStr">
         <is>
@@ -54261,17 +53313,15 @@
       <c r="O365" t="n">
         <v>0</v>
       </c>
+      <c r="P365" t="n">
+        <v>0</v>
+      </c>
       <c r="Q365" t="n">
         <v>0</v>
       </c>
       <c r="R365" t="n">
         <v>0</v>
       </c>
-      <c r="S365" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U365" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -54279,7 +53329,7 @@
       </c>
       <c r="AA365" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO365" t="inlineStr">
@@ -54289,12 +53339,7 @@
       </c>
       <c r="AP365" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ365" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS365" t="inlineStr">
@@ -54304,11 +53349,6 @@
       </c>
       <c r="AT365" t="n">
         <v>1</v>
-      </c>
-      <c r="AU365" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV365" t="inlineStr">
         <is>
@@ -54570,17 +53610,15 @@
       <c r="O367" t="n">
         <v>0</v>
       </c>
+      <c r="P367" t="n">
+        <v>0</v>
+      </c>
       <c r="Q367" t="n">
         <v>0</v>
       </c>
       <c r="R367" t="n">
         <v>0</v>
       </c>
-      <c r="S367" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U367" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -54588,7 +53626,7 @@
       </c>
       <c r="AA367" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO367" t="inlineStr">
@@ -54598,12 +53636,7 @@
       </c>
       <c r="AP367" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ367" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS367" t="inlineStr">
@@ -54613,11 +53646,6 @@
       </c>
       <c r="AT367" t="n">
         <v>1</v>
-      </c>
-      <c r="AU367" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV367" t="inlineStr">
         <is>
@@ -55290,17 +54318,15 @@
       <c r="O372" t="n">
         <v>0</v>
       </c>
+      <c r="P372" t="n">
+        <v>0</v>
+      </c>
       <c r="Q372" t="n">
         <v>0</v>
       </c>
       <c r="R372" t="n">
         <v>0</v>
       </c>
-      <c r="S372" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U372" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -55308,7 +54334,7 @@
       </c>
       <c r="AA372" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO372" t="inlineStr">
@@ -55318,12 +54344,7 @@
       </c>
       <c r="AP372" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ372" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS372" t="inlineStr">
@@ -55333,11 +54354,6 @@
       </c>
       <c r="AT372" t="n">
         <v>1</v>
-      </c>
-      <c r="AU372" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV372" t="inlineStr">
         <is>
@@ -55599,17 +54615,15 @@
       <c r="O374" t="n">
         <v>0</v>
       </c>
+      <c r="P374" t="n">
+        <v>0</v>
+      </c>
       <c r="Q374" t="n">
         <v>0</v>
       </c>
       <c r="R374" t="n">
         <v>0</v>
       </c>
-      <c r="S374" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U374" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -55617,7 +54631,7 @@
       </c>
       <c r="AA374" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO374" t="inlineStr">
@@ -55627,12 +54641,7 @@
       </c>
       <c r="AP374" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ374" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS374" t="inlineStr">
@@ -55642,11 +54651,6 @@
       </c>
       <c r="AT374" t="n">
         <v>1</v>
-      </c>
-      <c r="AU374" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV374" t="inlineStr">
         <is>
@@ -55908,17 +54912,15 @@
       <c r="O376" t="n">
         <v>0</v>
       </c>
+      <c r="P376" t="n">
+        <v>0</v>
+      </c>
       <c r="Q376" t="n">
         <v>0</v>
       </c>
       <c r="R376" t="n">
         <v>0</v>
       </c>
-      <c r="S376" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U376" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -55926,7 +54928,7 @@
       </c>
       <c r="AA376" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO376" t="inlineStr">
@@ -55936,12 +54938,7 @@
       </c>
       <c r="AP376" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ376" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS376" t="inlineStr">
@@ -55951,11 +54948,6 @@
       </c>
       <c r="AT376" t="n">
         <v>1</v>
-      </c>
-      <c r="AU376" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV376" t="inlineStr">
         <is>
@@ -56217,17 +55209,15 @@
       <c r="O378" t="n">
         <v>0</v>
       </c>
+      <c r="P378" t="n">
+        <v>0</v>
+      </c>
       <c r="Q378" t="n">
         <v>0</v>
       </c>
       <c r="R378" t="n">
         <v>0</v>
       </c>
-      <c r="S378" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U378" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -56235,7 +55225,7 @@
       </c>
       <c r="AA378" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO378" t="inlineStr">
@@ -56245,12 +55235,7 @@
       </c>
       <c r="AP378" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ378" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS378" t="inlineStr">
@@ -56260,11 +55245,6 @@
       </c>
       <c r="AT378" t="n">
         <v>1</v>
-      </c>
-      <c r="AU378" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV378" t="inlineStr">
         <is>
@@ -56937,17 +55917,15 @@
       <c r="O383" t="n">
         <v>0</v>
       </c>
+      <c r="P383" t="n">
+        <v>0</v>
+      </c>
       <c r="Q383" t="n">
         <v>0</v>
       </c>
       <c r="R383" t="n">
         <v>0</v>
       </c>
-      <c r="S383" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U383" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -56955,7 +55933,7 @@
       </c>
       <c r="AA383" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO383" t="inlineStr">
@@ -56965,12 +55943,7 @@
       </c>
       <c r="AP383" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ383" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS383" t="inlineStr">
@@ -56980,11 +55953,6 @@
       </c>
       <c r="AT383" t="n">
         <v>1</v>
-      </c>
-      <c r="AU383" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV383" t="inlineStr">
         <is>
@@ -57246,17 +56214,15 @@
       <c r="O385" t="n">
         <v>0</v>
       </c>
+      <c r="P385" t="n">
+        <v>0</v>
+      </c>
       <c r="Q385" t="n">
         <v>0</v>
       </c>
       <c r="R385" t="n">
         <v>0</v>
       </c>
-      <c r="S385" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U385" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -57264,7 +56230,7 @@
       </c>
       <c r="AA385" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO385" t="inlineStr">
@@ -57274,12 +56240,7 @@
       </c>
       <c r="AP385" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ385" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS385" t="inlineStr">
@@ -57289,11 +56250,6 @@
       </c>
       <c r="AT385" t="n">
         <v>1</v>
-      </c>
-      <c r="AU385" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV385" t="inlineStr">
         <is>
@@ -57555,17 +56511,15 @@
       <c r="O387" t="n">
         <v>0</v>
       </c>
+      <c r="P387" t="n">
+        <v>0</v>
+      </c>
       <c r="Q387" t="n">
         <v>0</v>
       </c>
       <c r="R387" t="n">
         <v>0</v>
       </c>
-      <c r="S387" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U387" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -57573,7 +56527,7 @@
       </c>
       <c r="AA387" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO387" t="inlineStr">
@@ -57583,12 +56537,7 @@
       </c>
       <c r="AP387" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ387" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS387" t="inlineStr">
@@ -57598,11 +56547,6 @@
       </c>
       <c r="AT387" t="n">
         <v>1</v>
-      </c>
-      <c r="AU387" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV387" t="inlineStr">
         <is>
@@ -57864,17 +56808,15 @@
       <c r="O389" t="n">
         <v>0</v>
       </c>
+      <c r="P389" t="n">
+        <v>0</v>
+      </c>
       <c r="Q389" t="n">
         <v>0</v>
       </c>
       <c r="R389" t="n">
         <v>0</v>
       </c>
-      <c r="S389" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U389" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -57882,7 +56824,7 @@
       </c>
       <c r="AA389" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO389" t="inlineStr">
@@ -57892,12 +56834,7 @@
       </c>
       <c r="AP389" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ389" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS389" t="inlineStr">
@@ -57907,11 +56844,6 @@
       </c>
       <c r="AT389" t="n">
         <v>1</v>
-      </c>
-      <c r="AU389" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV389" t="inlineStr">
         <is>
@@ -58173,17 +57105,15 @@
       <c r="O391" t="n">
         <v>0</v>
       </c>
+      <c r="P391" t="n">
+        <v>0</v>
+      </c>
       <c r="Q391" t="n">
         <v>0</v>
       </c>
       <c r="R391" t="n">
         <v>0</v>
       </c>
-      <c r="S391" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U391" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -58191,7 +57121,7 @@
       </c>
       <c r="AA391" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO391" t="inlineStr">
@@ -58201,12 +57131,7 @@
       </c>
       <c r="AP391" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ391" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS391" t="inlineStr">
@@ -58216,11 +57141,6 @@
       </c>
       <c r="AT391" t="n">
         <v>1</v>
-      </c>
-      <c r="AU391" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV391" t="inlineStr">
         <is>
@@ -58893,17 +57813,15 @@
       <c r="O396" t="n">
         <v>0</v>
       </c>
+      <c r="P396" t="n">
+        <v>0</v>
+      </c>
       <c r="Q396" t="n">
         <v>0</v>
       </c>
       <c r="R396" t="n">
         <v>0</v>
       </c>
-      <c r="S396" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U396" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -58911,7 +57829,7 @@
       </c>
       <c r="AA396" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO396" t="inlineStr">
@@ -58921,12 +57839,7 @@
       </c>
       <c r="AP396" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ396" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS396" t="inlineStr">
@@ -58936,11 +57849,6 @@
       </c>
       <c r="AT396" t="n">
         <v>1</v>
-      </c>
-      <c r="AU396" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV396" t="inlineStr">
         <is>
@@ -59202,17 +58110,15 @@
       <c r="O398" t="n">
         <v>0</v>
       </c>
+      <c r="P398" t="n">
+        <v>0</v>
+      </c>
       <c r="Q398" t="n">
         <v>0</v>
       </c>
       <c r="R398" t="n">
         <v>0</v>
       </c>
-      <c r="S398" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U398" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -59220,7 +58126,7 @@
       </c>
       <c r="AA398" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO398" t="inlineStr">
@@ -59230,12 +58136,7 @@
       </c>
       <c r="AP398" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ398" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS398" t="inlineStr">
@@ -59245,11 +58146,6 @@
       </c>
       <c r="AT398" t="n">
         <v>1</v>
-      </c>
-      <c r="AU398" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV398" t="inlineStr">
         <is>
@@ -59511,17 +58407,15 @@
       <c r="O400" t="n">
         <v>0</v>
       </c>
+      <c r="P400" t="n">
+        <v>0</v>
+      </c>
       <c r="Q400" t="n">
         <v>0</v>
       </c>
       <c r="R400" t="n">
         <v>0</v>
       </c>
-      <c r="S400" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U400" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -59529,7 +58423,7 @@
       </c>
       <c r="AA400" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO400" t="inlineStr">
@@ -59539,12 +58433,7 @@
       </c>
       <c r="AP400" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ400" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS400" t="inlineStr">
@@ -59554,11 +58443,6 @@
       </c>
       <c r="AT400" t="n">
         <v>1</v>
-      </c>
-      <c r="AU400" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV400" t="inlineStr">
         <is>
@@ -59820,17 +58704,15 @@
       <c r="O402" t="n">
         <v>0</v>
       </c>
+      <c r="P402" t="n">
+        <v>0</v>
+      </c>
       <c r="Q402" t="n">
         <v>0</v>
       </c>
       <c r="R402" t="n">
         <v>0</v>
       </c>
-      <c r="S402" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U402" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -59838,7 +58720,7 @@
       </c>
       <c r="AA402" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO402" t="inlineStr">
@@ -59848,12 +58730,7 @@
       </c>
       <c r="AP402" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ402" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS402" t="inlineStr">
@@ -59863,11 +58740,6 @@
       </c>
       <c r="AT402" t="n">
         <v>1</v>
-      </c>
-      <c r="AU402" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV402" t="inlineStr">
         <is>
@@ -60540,17 +59412,15 @@
       <c r="O407" t="n">
         <v>0</v>
       </c>
+      <c r="P407" t="n">
+        <v>0</v>
+      </c>
       <c r="Q407" t="n">
         <v>0</v>
       </c>
       <c r="R407" t="n">
         <v>0</v>
       </c>
-      <c r="S407" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U407" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -60558,7 +59428,7 @@
       </c>
       <c r="AA407" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO407" t="inlineStr">
@@ -60568,12 +59438,7 @@
       </c>
       <c r="AP407" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ407" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS407" t="inlineStr">
@@ -60583,11 +59448,6 @@
       </c>
       <c r="AT407" t="n">
         <v>1</v>
-      </c>
-      <c r="AU407" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV407" t="inlineStr">
         <is>
@@ -60849,17 +59709,15 @@
       <c r="O409" t="n">
         <v>0</v>
       </c>
+      <c r="P409" t="n">
+        <v>0</v>
+      </c>
       <c r="Q409" t="n">
         <v>0</v>
       </c>
       <c r="R409" t="n">
         <v>0</v>
       </c>
-      <c r="S409" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U409" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -60867,7 +59725,7 @@
       </c>
       <c r="AA409" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO409" t="inlineStr">
@@ -60877,12 +59735,7 @@
       </c>
       <c r="AP409" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ409" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS409" t="inlineStr">
@@ -60892,11 +59745,6 @@
       </c>
       <c r="AT409" t="n">
         <v>1</v>
-      </c>
-      <c r="AU409" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV409" t="inlineStr">
         <is>
@@ -61158,17 +60006,15 @@
       <c r="O411" t="n">
         <v>0</v>
       </c>
+      <c r="P411" t="n">
+        <v>0</v>
+      </c>
       <c r="Q411" t="n">
         <v>0</v>
       </c>
       <c r="R411" t="n">
         <v>0</v>
       </c>
-      <c r="S411" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U411" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -61176,7 +60022,7 @@
       </c>
       <c r="AA411" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO411" t="inlineStr">
@@ -61186,12 +60032,7 @@
       </c>
       <c r="AP411" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ411" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS411" t="inlineStr">
@@ -61201,11 +60042,6 @@
       </c>
       <c r="AT411" t="n">
         <v>1</v>
-      </c>
-      <c r="AU411" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV411" t="inlineStr">
         <is>
@@ -61467,17 +60303,15 @@
       <c r="O413" t="n">
         <v>0</v>
       </c>
+      <c r="P413" t="n">
+        <v>0</v>
+      </c>
       <c r="Q413" t="n">
         <v>0</v>
       </c>
       <c r="R413" t="n">
         <v>0</v>
       </c>
-      <c r="S413" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U413" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -61485,7 +60319,7 @@
       </c>
       <c r="AA413" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO413" t="inlineStr">
@@ -61495,12 +60329,7 @@
       </c>
       <c r="AP413" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ413" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS413" t="inlineStr">
@@ -61510,11 +60339,6 @@
       </c>
       <c r="AT413" t="n">
         <v>1</v>
-      </c>
-      <c r="AU413" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV413" t="inlineStr">
         <is>
@@ -62052,17 +60876,15 @@
       <c r="O417" t="n">
         <v>0</v>
       </c>
+      <c r="P417" t="n">
+        <v>0</v>
+      </c>
       <c r="Q417" t="n">
         <v>0</v>
       </c>
       <c r="R417" t="n">
         <v>0</v>
       </c>
-      <c r="S417" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U417" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -62070,7 +60892,7 @@
       </c>
       <c r="AA417" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO417" t="inlineStr">
@@ -62080,12 +60902,7 @@
       </c>
       <c r="AP417" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ417" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS417" t="inlineStr">
@@ -62095,11 +60912,6 @@
       </c>
       <c r="AT417" t="n">
         <v>1</v>
-      </c>
-      <c r="AU417" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV417" t="inlineStr">
         <is>
@@ -62496,17 +61308,15 @@
       <c r="O420" t="n">
         <v>0</v>
       </c>
+      <c r="P420" t="n">
+        <v>0</v>
+      </c>
       <c r="Q420" t="n">
         <v>0</v>
       </c>
       <c r="R420" t="n">
         <v>0</v>
       </c>
-      <c r="S420" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U420" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -62514,7 +61324,7 @@
       </c>
       <c r="AA420" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO420" t="inlineStr">
@@ -62524,12 +61334,7 @@
       </c>
       <c r="AP420" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ420" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS420" t="inlineStr">
@@ -62539,11 +61344,6 @@
       </c>
       <c r="AT420" t="n">
         <v>1</v>
-      </c>
-      <c r="AU420" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV420" t="inlineStr">
         <is>
@@ -62805,17 +61605,15 @@
       <c r="O422" t="n">
         <v>0</v>
       </c>
+      <c r="P422" t="n">
+        <v>0</v>
+      </c>
       <c r="Q422" t="n">
         <v>0</v>
       </c>
       <c r="R422" t="n">
         <v>0</v>
       </c>
-      <c r="S422" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U422" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -62823,7 +61621,7 @@
       </c>
       <c r="AA422" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO422" t="inlineStr">
@@ -62833,12 +61631,7 @@
       </c>
       <c r="AP422" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ422" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS422" t="inlineStr">
@@ -62848,11 +61641,6 @@
       </c>
       <c r="AT422" t="n">
         <v>1</v>
-      </c>
-      <c r="AU422" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV422" t="inlineStr">
         <is>
@@ -63114,17 +61902,15 @@
       <c r="O424" t="n">
         <v>0</v>
       </c>
+      <c r="P424" t="n">
+        <v>0</v>
+      </c>
       <c r="Q424" t="n">
         <v>0</v>
       </c>
       <c r="R424" t="n">
         <v>0</v>
       </c>
-      <c r="S424" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U424" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -63132,7 +61918,7 @@
       </c>
       <c r="AA424" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO424" t="inlineStr">
@@ -63142,12 +61928,7 @@
       </c>
       <c r="AP424" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ424" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS424" t="inlineStr">
@@ -63157,11 +61938,6 @@
       </c>
       <c r="AT424" t="n">
         <v>1</v>
-      </c>
-      <c r="AU424" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV424" t="inlineStr">
         <is>
@@ -63423,17 +62199,15 @@
       <c r="O426" t="n">
         <v>0</v>
       </c>
+      <c r="P426" t="n">
+        <v>0</v>
+      </c>
       <c r="Q426" t="n">
         <v>0</v>
       </c>
       <c r="R426" t="n">
         <v>0</v>
       </c>
-      <c r="S426" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U426" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -63441,7 +62215,7 @@
       </c>
       <c r="AA426" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO426" t="inlineStr">
@@ -63451,12 +62225,7 @@
       </c>
       <c r="AP426" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ426" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS426" t="inlineStr">
@@ -63466,11 +62235,6 @@
       </c>
       <c r="AT426" t="n">
         <v>1</v>
-      </c>
-      <c r="AU426" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV426" t="inlineStr">
         <is>
@@ -64143,17 +62907,15 @@
       <c r="O431" t="n">
         <v>0</v>
       </c>
+      <c r="P431" t="n">
+        <v>0</v>
+      </c>
       <c r="Q431" t="n">
         <v>0</v>
       </c>
       <c r="R431" t="n">
         <v>0</v>
       </c>
-      <c r="S431" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U431" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -64161,7 +62923,7 @@
       </c>
       <c r="AA431" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO431" t="inlineStr">
@@ -64171,12 +62933,7 @@
       </c>
       <c r="AP431" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ431" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS431" t="inlineStr">
@@ -64186,11 +62943,6 @@
       </c>
       <c r="AT431" t="n">
         <v>1</v>
-      </c>
-      <c r="AU431" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV431" t="inlineStr">
         <is>
@@ -64452,17 +63204,15 @@
       <c r="O433" t="n">
         <v>0</v>
       </c>
+      <c r="P433" t="n">
+        <v>0</v>
+      </c>
       <c r="Q433" t="n">
         <v>0</v>
       </c>
       <c r="R433" t="n">
         <v>0</v>
       </c>
-      <c r="S433" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U433" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -64470,7 +63220,7 @@
       </c>
       <c r="AA433" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO433" t="inlineStr">
@@ -64480,12 +63230,7 @@
       </c>
       <c r="AP433" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ433" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS433" t="inlineStr">
@@ -64495,11 +63240,6 @@
       </c>
       <c r="AT433" t="n">
         <v>1</v>
-      </c>
-      <c r="AU433" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV433" t="inlineStr">
         <is>
@@ -64761,17 +63501,15 @@
       <c r="O435" t="n">
         <v>0</v>
       </c>
+      <c r="P435" t="n">
+        <v>0</v>
+      </c>
       <c r="Q435" t="n">
         <v>0</v>
       </c>
       <c r="R435" t="n">
         <v>0</v>
       </c>
-      <c r="S435" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U435" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -64779,7 +63517,7 @@
       </c>
       <c r="AA435" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO435" t="inlineStr">
@@ -64789,12 +63527,7 @@
       </c>
       <c r="AP435" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ435" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS435" t="inlineStr">
@@ -64804,11 +63537,6 @@
       </c>
       <c r="AT435" t="n">
         <v>1</v>
-      </c>
-      <c r="AU435" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV435" t="inlineStr">
         <is>
@@ -65070,17 +63798,15 @@
       <c r="O437" t="n">
         <v>0</v>
       </c>
+      <c r="P437" t="n">
+        <v>0</v>
+      </c>
       <c r="Q437" t="n">
         <v>0</v>
       </c>
       <c r="R437" t="n">
         <v>0</v>
       </c>
-      <c r="S437" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U437" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -65088,7 +63814,7 @@
       </c>
       <c r="AA437" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO437" t="inlineStr">
@@ -65098,12 +63824,7 @@
       </c>
       <c r="AP437" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ437" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS437" t="inlineStr">
@@ -65113,11 +63834,6 @@
       </c>
       <c r="AT437" t="n">
         <v>1</v>
-      </c>
-      <c r="AU437" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV437" t="inlineStr">
         <is>
@@ -65790,17 +64506,15 @@
       <c r="O442" t="n">
         <v>0</v>
       </c>
+      <c r="P442" t="n">
+        <v>0</v>
+      </c>
       <c r="Q442" t="n">
         <v>0</v>
       </c>
       <c r="R442" t="n">
         <v>0</v>
       </c>
-      <c r="S442" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U442" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -65808,7 +64522,7 @@
       </c>
       <c r="AA442" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO442" t="inlineStr">
@@ -65818,12 +64532,7 @@
       </c>
       <c r="AP442" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ442" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS442" t="inlineStr">
@@ -65833,11 +64542,6 @@
       </c>
       <c r="AT442" t="n">
         <v>1</v>
-      </c>
-      <c r="AU442" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV442" t="inlineStr">
         <is>
@@ -66099,17 +64803,15 @@
       <c r="O444" t="n">
         <v>0</v>
       </c>
+      <c r="P444" t="n">
+        <v>0</v>
+      </c>
       <c r="Q444" t="n">
         <v>0</v>
       </c>
       <c r="R444" t="n">
         <v>0</v>
       </c>
-      <c r="S444" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U444" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -66117,7 +64819,7 @@
       </c>
       <c r="AA444" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO444" t="inlineStr">
@@ -66127,12 +64829,7 @@
       </c>
       <c r="AP444" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ444" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS444" t="inlineStr">
@@ -66142,11 +64839,6 @@
       </c>
       <c r="AT444" t="n">
         <v>1</v>
-      </c>
-      <c r="AU444" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV444" t="inlineStr">
         <is>
@@ -66408,17 +65100,15 @@
       <c r="O446" t="n">
         <v>0</v>
       </c>
+      <c r="P446" t="n">
+        <v>0</v>
+      </c>
       <c r="Q446" t="n">
         <v>0</v>
       </c>
       <c r="R446" t="n">
         <v>0</v>
       </c>
-      <c r="S446" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U446" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -66426,7 +65116,7 @@
       </c>
       <c r="AA446" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO446" t="inlineStr">
@@ -66436,12 +65126,7 @@
       </c>
       <c r="AP446" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ446" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS446" t="inlineStr">
@@ -66451,11 +65136,6 @@
       </c>
       <c r="AT446" t="n">
         <v>1</v>
-      </c>
-      <c r="AU446" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV446" t="inlineStr">
         <is>
@@ -66717,17 +65397,15 @@
       <c r="O448" t="n">
         <v>0</v>
       </c>
+      <c r="P448" t="n">
+        <v>0</v>
+      </c>
       <c r="Q448" t="n">
         <v>0</v>
       </c>
       <c r="R448" t="n">
         <v>0</v>
       </c>
-      <c r="S448" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U448" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -66735,7 +65413,7 @@
       </c>
       <c r="AA448" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO448" t="inlineStr">
@@ -66745,12 +65423,7 @@
       </c>
       <c r="AP448" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ448" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS448" t="inlineStr">
@@ -66760,11 +65433,6 @@
       </c>
       <c r="AT448" t="n">
         <v>1</v>
-      </c>
-      <c r="AU448" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV448" t="inlineStr">
         <is>
@@ -67026,17 +65694,15 @@
       <c r="O450" t="n">
         <v>0</v>
       </c>
+      <c r="P450" t="n">
+        <v>0</v>
+      </c>
       <c r="Q450" t="n">
         <v>0</v>
       </c>
       <c r="R450" t="n">
         <v>0</v>
       </c>
-      <c r="S450" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U450" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -67044,7 +65710,7 @@
       </c>
       <c r="AA450" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO450" t="inlineStr">
@@ -67054,12 +65720,7 @@
       </c>
       <c r="AP450" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ450" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS450" t="inlineStr">
@@ -67069,11 +65730,6 @@
       </c>
       <c r="AT450" t="n">
         <v>1</v>
-      </c>
-      <c r="AU450" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV450" t="inlineStr">
         <is>
@@ -67746,17 +66402,15 @@
       <c r="O455" t="n">
         <v>0</v>
       </c>
+      <c r="P455" t="n">
+        <v>0</v>
+      </c>
       <c r="Q455" t="n">
         <v>0</v>
       </c>
       <c r="R455" t="n">
         <v>0</v>
       </c>
-      <c r="S455" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U455" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -67764,7 +66418,7 @@
       </c>
       <c r="AA455" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO455" t="inlineStr">
@@ -67774,12 +66428,7 @@
       </c>
       <c r="AP455" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ455" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS455" t="inlineStr">
@@ -67789,11 +66438,6 @@
       </c>
       <c r="AT455" t="n">
         <v>1</v>
-      </c>
-      <c r="AU455" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV455" t="inlineStr">
         <is>
@@ -68055,17 +66699,15 @@
       <c r="O457" t="n">
         <v>0</v>
       </c>
+      <c r="P457" t="n">
+        <v>0</v>
+      </c>
       <c r="Q457" t="n">
         <v>0</v>
       </c>
       <c r="R457" t="n">
         <v>0</v>
       </c>
-      <c r="S457" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U457" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -68073,7 +66715,7 @@
       </c>
       <c r="AA457" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO457" t="inlineStr">
@@ -68083,12 +66725,7 @@
       </c>
       <c r="AP457" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ457" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS457" t="inlineStr">
@@ -68098,11 +66735,6 @@
       </c>
       <c r="AT457" t="n">
         <v>1</v>
-      </c>
-      <c r="AU457" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV457" t="inlineStr">
         <is>
@@ -68364,17 +66996,15 @@
       <c r="O459" t="n">
         <v>0</v>
       </c>
+      <c r="P459" t="n">
+        <v>0</v>
+      </c>
       <c r="Q459" t="n">
         <v>0</v>
       </c>
       <c r="R459" t="n">
         <v>0</v>
       </c>
-      <c r="S459" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U459" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -68382,7 +67012,7 @@
       </c>
       <c r="AA459" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO459" t="inlineStr">
@@ -68392,12 +67022,7 @@
       </c>
       <c r="AP459" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ459" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS459" t="inlineStr">
@@ -68407,11 +67032,6 @@
       </c>
       <c r="AT459" t="n">
         <v>1</v>
-      </c>
-      <c r="AU459" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV459" t="inlineStr">
         <is>
@@ -68673,17 +67293,15 @@
       <c r="O461" t="n">
         <v>0</v>
       </c>
+      <c r="P461" t="n">
+        <v>0</v>
+      </c>
       <c r="Q461" t="n">
         <v>0</v>
       </c>
       <c r="R461" t="n">
         <v>0</v>
       </c>
-      <c r="S461" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U461" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -68691,7 +67309,7 @@
       </c>
       <c r="AA461" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO461" t="inlineStr">
@@ -68701,12 +67319,7 @@
       </c>
       <c r="AP461" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ461" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS461" t="inlineStr">
@@ -68716,11 +67329,6 @@
       </c>
       <c r="AT461" t="n">
         <v>1</v>
-      </c>
-      <c r="AU461" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV461" t="inlineStr">
         <is>
@@ -69393,17 +68001,15 @@
       <c r="O466" t="n">
         <v>0</v>
       </c>
+      <c r="P466" t="n">
+        <v>0</v>
+      </c>
       <c r="Q466" t="n">
         <v>0</v>
       </c>
       <c r="R466" t="n">
         <v>0</v>
       </c>
-      <c r="S466" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U466" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -69411,7 +68017,7 @@
       </c>
       <c r="AA466" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO466" t="inlineStr">
@@ -69421,12 +68027,7 @@
       </c>
       <c r="AP466" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ466" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS466" t="inlineStr">
@@ -69436,11 +68037,6 @@
       </c>
       <c r="AT466" t="n">
         <v>1</v>
-      </c>
-      <c r="AU466" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV466" t="inlineStr">
         <is>
@@ -69702,17 +68298,15 @@
       <c r="O468" t="n">
         <v>0</v>
       </c>
+      <c r="P468" t="n">
+        <v>0</v>
+      </c>
       <c r="Q468" t="n">
         <v>0</v>
       </c>
       <c r="R468" t="n">
         <v>0</v>
       </c>
-      <c r="S468" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U468" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -69720,7 +68314,7 @@
       </c>
       <c r="AA468" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO468" t="inlineStr">
@@ -69730,12 +68324,7 @@
       </c>
       <c r="AP468" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ468" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS468" t="inlineStr">
@@ -69745,11 +68334,6 @@
       </c>
       <c r="AT468" t="n">
         <v>1</v>
-      </c>
-      <c r="AU468" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV468" t="inlineStr">
         <is>
@@ -70011,17 +68595,15 @@
       <c r="O470" t="n">
         <v>0</v>
       </c>
+      <c r="P470" t="n">
+        <v>0</v>
+      </c>
       <c r="Q470" t="n">
         <v>0</v>
       </c>
       <c r="R470" t="n">
         <v>0</v>
       </c>
-      <c r="S470" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U470" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -70029,7 +68611,7 @@
       </c>
       <c r="AA470" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO470" t="inlineStr">
@@ -70039,12 +68621,7 @@
       </c>
       <c r="AP470" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ470" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS470" t="inlineStr">
@@ -70054,11 +68631,6 @@
       </c>
       <c r="AT470" t="n">
         <v>1</v>
-      </c>
-      <c r="AU470" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV470" t="inlineStr">
         <is>
@@ -70320,17 +68892,15 @@
       <c r="O472" t="n">
         <v>0</v>
       </c>
+      <c r="P472" t="n">
+        <v>0</v>
+      </c>
       <c r="Q472" t="n">
         <v>0</v>
       </c>
       <c r="R472" t="n">
         <v>0</v>
       </c>
-      <c r="S472" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U472" t="inlineStr">
         <is>
           <t>HOLD_JP_946889c1802490e85f0687e31732</t>
@@ -70338,7 +68908,7 @@
       </c>
       <c r="AA472" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO472" t="inlineStr">
@@ -70348,12 +68918,7 @@
       </c>
       <c r="AP472" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ472" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS472" t="inlineStr">
@@ -70363,11 +68928,6 @@
       </c>
       <c r="AT472" t="n">
         <v>1</v>
-      </c>
-      <c r="AU472" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV472" t="inlineStr">
         <is>
